--- a/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -344,7 +344,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActPriority-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActPriority-cisis|20260916095455</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}

--- a/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
